--- a/artfynd/A 37641-2026 artfynd.xlsx
+++ b/artfynd/A 37641-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,9 +784,888 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137257092</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58036</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>V Skogstorp N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>516483</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6633233</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 obs 29 sept, 2 obs 30 sept</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137257092</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137257020</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>V Skogstorp N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516483</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6633233</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>enstaka obs  under 2 av 6 dagar</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137257020</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137257303</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100137</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Slaguggla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Strix uralensis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pallas, 1771</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>V Skogstorp N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516483</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6633233</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Upprepat kontaktläte, troligen hona, 02 oktober. Det förekommer även  flera andra läten andra dagar, som möjligen är slaguggla, men de är mera svårbestämda,</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137257303</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137233086</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57201</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>V Skogstorp N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516483</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6633233</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7 st tydliga spelläten 28 sept</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Örebro län LB</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137233086</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137257003</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57855</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>V Skogstorp N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516483</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6633233</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>obs 29 september</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137257003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137257011</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58182</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>V Skogstorp N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516483</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6633233</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka obs 2-3 av 6 dagar</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137257011</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137257015</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58184</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>V Skogstorp N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516483</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6633233</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Många obs 5 av 6 dagar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137257015</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37641-2026 artfynd.xlsx
+++ b/artfynd/A 37641-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137257092</v>
       </c>
       <c r="B3" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137257020</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
+          <t>Maria Berdén Evertsson, Per Arneborn, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1037,7 +1037,7 @@
         <v>137257303</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>137233086</v>
       </c>
       <c r="B6" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>137257003</v>
       </c>
       <c r="B7" t="n">
-        <v>57855</v>
+        <v>57865</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
+          <t>Maria Berdén Evertsson, Per Arneborn, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1413,7 +1413,7 @@
         <v>137257011</v>
       </c>
       <c r="B8" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
+          <t>Maria Berdén Evertsson, Per Arneborn, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1537,7 +1537,7 @@
         <v>137257015</v>
       </c>
       <c r="B9" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
+          <t>Maria Berdén Evertsson, Per Arneborn, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 37641-2026 artfynd.xlsx
+++ b/artfynd/A 37641-2026 artfynd.xlsx
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Berdén Evertsson, Per Arneborn, Lotta Sörman</t>
+          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Berdén Evertsson, Per Arneborn, Lotta Sörman</t>
+          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Berdén Evertsson, Per Arneborn, Lotta Sörman</t>
+          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Berdén Evertsson, Per Arneborn, Lotta Sörman</t>
+          <t>Maria Berdén Evertsson, Lotta Sörman, Per Arneborn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 37641-2026 artfynd.xlsx
+++ b/artfynd/A 37641-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137257092</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137257020</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>137257303</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>137233086</v>
       </c>
       <c r="B6" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>137257003</v>
       </c>
       <c r="B7" t="n">
-        <v>57865</v>
+        <v>57866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137257011</v>
       </c>
       <c r="B8" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>137257015</v>
       </c>
       <c r="B9" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37641-2026 artfynd.xlsx
+++ b/artfynd/A 37641-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137257092</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137257020</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>137257303</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137257011</v>
       </c>
       <c r="B8" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>137257015</v>
       </c>
       <c r="B9" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37641-2026 artfynd.xlsx
+++ b/artfynd/A 37641-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137257092</v>
       </c>
       <c r="B3" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137257020</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>137257303</v>
       </c>
       <c r="B5" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>137233086</v>
       </c>
       <c r="B6" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>137257003</v>
       </c>
       <c r="B7" t="n">
-        <v>57866</v>
+        <v>57869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137257011</v>
       </c>
       <c r="B8" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>137257015</v>
       </c>
       <c r="B9" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
